--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.4.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.4.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00126_19130805.4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.N_00126_19130805.4" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.4.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.4.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -975,7 +975,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.4.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.4.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.N_00126_19130805.4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00126_19130805.4" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y103"/>
+  <dimension ref="A1:Y106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L20: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ " -</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L8: isolated marker/symbol line :: A</t>
@@ -630,7 +634,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -646,7 +650,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L521: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | line starts with punctuation glued to text :: .for the very generous patronage you have given me since I opened up myâ€¢</t>
+          <t>L520: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • TO MY PATRONS-I wish to take this op- • nity of thanking you•</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -677,7 +681,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>781</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -689,7 +693,7 @@
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>L1081: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | localized OCR phrase divergence vs other OCR: "ofr" vs "of publication Hall s e MEATS AND Fi38" :: later than 9 a. m. on the day of â€¢</t>
+          <t>L1081: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | localized OCR phrase divergence vs other OCR: "ofr" vs "of publication Hall’s e MEATS AND Fi38" :: later than 9 a. m. on the day of •</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
@@ -704,12 +708,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L113: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ST. STEPHEN â€”</t>
+          <t>L289: stray/suspicious non-ASCII glyph(s): U+7535 CJK UNIFIED IDEOGRAPH-7535 | isolated marker/symbol line :: 电</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L33: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: goilâ€™s</t>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • " -</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -737,7 +741,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L524: line starts with punctuation glued to text :: .been a source of great -gement to me, but has permitted me toe</t>
+          <t>L521: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: .for the very generous patronage you have given me since I opened up my•</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -783,19 +787,19 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: " KLEANALLâ€�</t>
+          <t>L374: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | symbol-only separator/garbage line :: ： 36</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: countryâ€™s economic deliverance. By</t>
+          <t>L117: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: for a maternity branch • of Hosp tal</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L64: symbol-only separator/garbage line :: 215-11</t>
+          <t>L20: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -816,7 +820,7 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L1012: symbol-only separator/garbage line | line starts with punctuation glued to text :: * 600</t>
+          <t>L522: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Millinery Parlors in this city. The very sanguine way in which your sup- Y</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -834,12 +838,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>159</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>174</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -862,24 +866,24 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L205: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: New York, Aug. 5.â€” The opening</t>
+          <t>L405: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Trustees Heard Suggestions at Monthly Meeting</t>
+          <t>L520: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • TO MY PATRONS-I wish to take this op- • nity of thanking you•</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L69: symbol-only separator/garbage line :: 215-31</t>
+          <t>L64: symbol-only separator/garbage line :: 215-11</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L30: isolated marker/symbol line :: &gt;</t>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • " -</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -889,11 +893,15 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L588: punctuation artifact: repeated periods :: Am. Copper........</t>
+          <t>L520: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • TO MY PATRONS-I wish to take this op- • nity of thanking you•</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L523: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • port has been given has surpassed my fullest expectations and has not only•</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -933,24 +941,24 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L264: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: will kindly leave at Gleaner office â€” 1 in</t>
+          <t>L470: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | symbol-only separator/garbage line | punctuation artifact: repeated periods :: ：... 15%</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Yesterdayâ€”New Annex to Cost About $12,000,</t>
+          <t>L521: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: .for the very generous patronage you have given me since I opened up my•</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: 368</t>
+          <t>L69: symbol-only separator/garbage line :: 215-31</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: a</t>
+          <t>L30: isolated marker/symbol line :: &gt;</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
@@ -960,11 +968,15 @@
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L590: punctuation artifact: repeated periods :: Am. Beet Sugar..</t>
+          <t>L588: punctuation artifact: repeated periods :: Am. Copper........</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>L524: line starts with punctuation glued to text :: .been a source of great -gement to me, but has permitted me toe</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
@@ -1004,24 +1016,24 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L306: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): PATRoNs (odd internal casing) :: To MY PATRoNs â€” I wish to take this Opr Â· nity of thanking you</t>
+          <t>L536: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: poâ€™nts about the best way to change</t>
+          <t>L522: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Millinery Parlors in this city. The very sanguine way in which your sup- Y</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L74: isolated marker/symbol line :: 368</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 1</t>
+          <t>L41: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -1031,11 +1043,15 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L601: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 71</t>
+          <t>L590: punctuation artifact: repeated periods :: Am. Beet Sugar..</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
-      <c r="S7" s="1" t="inlineStr"/>
+      <c r="S7" s="1" t="inlineStr">
+        <is>
+          <t>L525: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •select my stock for Fall from the leading British and American Millinery.</t>
+        </is>
+      </c>
       <c r="T7" s="1" t="inlineStr"/>
       <c r="U7" s="1" t="inlineStr"/>
       <c r="V7" s="1" t="inlineStr"/>
@@ -1075,24 +1091,24 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L389: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 75c (letter/digit mix) :: Pricesâ€”75c, $1. $ 1.00, $ 1.50.</t>
+          <t>L612: stray/suspicious non-ASCII glyph(s): U+6E90 CJK UNIFIED IDEOGRAPH-6E90 | isolated marker/symbol line :: 源</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L117: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: for a maternity branch â€¢ of Hosp tal</t>
+          <t>L523: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • port has been given has surpassed my fullest expectations and has not only•</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L186: isolated marker/symbol line :: *</t>
+          <t>L101: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 4</t>
+          <t>L43: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -1102,11 +1118,15 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L603: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 26%</t>
+          <t>L601: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 71</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
-      <c r="S8" s="1" t="inlineStr"/>
+      <c r="S8" s="1" t="inlineStr">
+        <is>
+          <t>L526: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •centerusting to be favored with a continuance of your esteemed patronage,.</t>
+        </is>
+      </c>
       <c r="T8" s="1" t="inlineStr"/>
       <c r="U8" s="1" t="inlineStr"/>
       <c r="V8" s="1" t="inlineStr"/>
@@ -1136,7 +1156,7 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>L306: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): PATRoNs (odd internal casing) :: To MY PATRoNs â€” I wish to take this Opr Â· nity of thanking you</t>
+          <t>L306: suspicious token(s): PATRoNs (odd internal casing) :: To MY PATRoNs — I wish to take this Opr · nity of thanking you</t>
         </is>
       </c>
       <c r="I9" s="1" t="inlineStr">
@@ -1146,24 +1166,24 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L411: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦â€¦</t>
+          <t>L642: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: Cement-275 at 32 ， 20 at 32%, 65</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L208: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: enclosed $25 from St. Annâ€™s Church</t>
+          <t>L525: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •select my stock for Fall from the leading British and American Millinery.</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L248: isolated marker/symbol line :: 2</t>
+          <t>L186: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: -</t>
+          <t>L53: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr">
@@ -1173,11 +1193,15 @@
       </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>L605: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 4%</t>
+          <t>L603: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 26%</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr"/>
-      <c r="S9" s="1" t="inlineStr"/>
+      <c r="S9" s="1" t="inlineStr">
+        <is>
+          <t>L528: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Yours Very Respectfully,</t>
+        </is>
+      </c>
       <c r="T9" s="1" t="inlineStr"/>
       <c r="U9" s="1" t="inlineStr"/>
       <c r="V9" s="1" t="inlineStr"/>
@@ -1193,12 +1217,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1212,29 +1236,29 @@
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>L728: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 75c (letter/digit mix) :: Pricesâ€”75c, $1.00, $1.50.</t>
+          <t>L728: suspicious token(s): 75c (letter/digit mix) :: Prices—75c, $1.00, $1.50.</t>
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L500: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: MAPLE "CREMOâ€� FROSTING</t>
+          <t>L679: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L221: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ST. JOHNâ€”</t>
+          <t>L526: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •centerusting to be favored with a continuance of your esteemed patronage,.</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L263: symbol-only separator/garbage line :: 613.</t>
+          <t>L248: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: )</t>
+          <t>L55: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -1244,11 +1268,15 @@
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>L607: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...42%</t>
+          <t>L605: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 4%</t>
         </is>
       </c>
       <c r="R10" s="1" t="inlineStr"/>
-      <c r="S10" s="1" t="inlineStr"/>
+      <c r="S10" s="1" t="inlineStr">
+        <is>
+          <t>L1012: symbol-only separator/garbage line | line starts with punctuation glued to text :: * 600</t>
+        </is>
+      </c>
       <c r="T10" s="1" t="inlineStr"/>
       <c r="U10" s="1" t="inlineStr"/>
       <c r="V10" s="1" t="inlineStr"/>
@@ -1269,7 +1297,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1278,7 +1306,7 @@
       <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>L389: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 75c (letter/digit mix) :: Pricesâ€”75c, $1. $ 1.00, $ 1.50.</t>
+          <t>L389: suspicious token(s): 75c (letter/digit mix) :: Prices—75c, $1. $ 1.00, $ 1.50.</t>
         </is>
       </c>
       <c r="I11" s="1" t="inlineStr">
@@ -1288,24 +1316,24 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L546: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦.</t>
+          <t>L768: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L230: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WOODSTOCKâ€”</t>
+          <t>L528: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Yours Very Respectfully,</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L320: isolated marker/symbol line :: 71</t>
+          <t>L263: symbol-only separator/garbage line :: 613.</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 2</t>
+          <t>L84: isolated marker/symbol line :: )</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr">
@@ -1315,11 +1343,15 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>L609: punctuation artifact: repeated periods :: Am. Cot. Oil......</t>
+          <t>L607: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...42%</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
-      <c r="S11" s="1" t="inlineStr"/>
+      <c r="S11" s="1" t="inlineStr">
+        <is>
+          <t>L1079: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •ing made in advertisements,•</t>
+        </is>
+      </c>
       <c r="T11" s="1" t="inlineStr"/>
       <c r="U11" s="1" t="inlineStr"/>
       <c r="V11" s="1" t="inlineStr"/>
@@ -1335,12 +1367,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>105</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1357,26 +1389,22 @@
           <t>L879: suspicious token(s): theLaurier (odd internal casing) | likely joined words/missing space :: tice of theLaurier Government early</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L612: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: æº�</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L232: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Guy L. Hansonâ€™s Bookstore, Queen St.</t>
+          <t>L671: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L332: symbol-only separator/garbage line :: 27%</t>
+          <t>L289: stray/suspicious non-ASCII glyph(s): U+7535 CJK UNIFIED IDEOGRAPH-7535 | isolated marker/symbol line :: 电</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L92: symbol-only separator/garbage line :: 1107</t>
+          <t>L90: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr">
@@ -1386,11 +1414,15 @@
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>L611: punctuation artifact: repeated periods :: Am. Loco..........</t>
+          <t>L609: punctuation artifact: repeated periods :: Am. Cot. Oil......</t>
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr"/>
-      <c r="S12" s="1" t="inlineStr"/>
+      <c r="S12" s="1" t="inlineStr">
+        <is>
+          <t>L1083: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • publication.•</t>
+        </is>
+      </c>
       <c r="T12" s="1" t="inlineStr"/>
       <c r="U12" s="1" t="inlineStr"/>
       <c r="V12" s="1" t="inlineStr"/>
@@ -1411,7 +1443,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1428,26 +1460,22 @@
           <t>L959: suspicious token(s): VanWart (odd internal casing) :: Dr. VanWart presided at the meet-</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L623: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Crown â€” 2, 070 at 275, 100 at 279, 25</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: OTTAWAâ€”</t>
+          <t>L1078: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: ♦ in order to ensure changes be-•</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L338: isolated marker/symbol line :: 45</t>
+          <t>L320: isolated marker/symbol line :: 71</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: A</t>
+          <t>L92: symbol-only separator/garbage line :: 1107</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr">
@@ -1457,7 +1485,7 @@
       </c>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>L613: punctuation artifact: repeated periods :: Am. Sm. and Ref..</t>
+          <t>L611: punctuation artifact: repeated periods :: Am. Loco..........</t>
         </is>
       </c>
       <c r="R13" s="1" t="inlineStr"/>
@@ -1482,7 +1510,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1496,25 +1524,25 @@
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>L1068: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 4a (letter/digit mix) :: â€”4a t 215; Nova Scotiaâ€”1.1 at 251;</t>
+          <t>L1068: suspicious token(s): 4a (letter/digit mix) :: —4a t 215; Nova Scotia—1.1 at 251;</t>
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L252: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: BANGOR, ME.â€”</t>
+          <t>L1079: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •ing made in advertisements,•</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L344: isolated marker/symbol line :: 1</t>
+          <t>L332: symbol-only separator/garbage line :: 27%</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: *</t>
+          <t>L96: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr">
@@ -1524,7 +1552,7 @@
       </c>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>L617: punctuation artifact: repeated periods :: Am. Sugar..........</t>
+          <t>L613: punctuation artifact: repeated periods :: Am. Sm. and Ref..</t>
         </is>
       </c>
       <c r="R14" s="1" t="inlineStr"/>
@@ -1569,19 +1597,19 @@
       <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L257: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: HOULTON, ME.â€”</t>
+          <t>L1080: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET :: ♦ copy must reach this office not •</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L345: symbol-only separator/garbage line :: 43%</t>
+          <t>L338: isolated marker/symbol line :: 45</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: %</t>
+          <t>L101: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr">
@@ -1591,7 +1619,7 @@
       </c>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>L619: punctuation artifact: repeated periods :: An. Copper........</t>
+          <t>L617: punctuation artifact: repeated periods :: Am. Sugar..........</t>
         </is>
       </c>
       <c r="R15" s="1" t="inlineStr"/>
@@ -1628,19 +1656,19 @@
       <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L269: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: say that hâ€™s Government would not</t>
+          <t>L1081: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | localized OCR phrase divergence vs other OCR: "ofr" vs "of publication Hall’s e MEATS AND Fi38" :: later than 9 a. m. on the day of •</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L353: isolated marker/symbol line :: 31</t>
+          <t>L344: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L223: isolated marker/symbol line :: L.</t>
+          <t>L103: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr">
@@ -1650,7 +1678,7 @@
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>L621: punctuation artifact: repeated periods :: Atchison...........</t>
+          <t>L619: punctuation artifact: repeated periods :: An. Copper........</t>
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr"/>
@@ -1687,19 +1715,19 @@
       <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>L337: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ladiesâ€™ committee have now $1,000.</t>
+          <t>L1083: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • publication.•</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L356: symbol-only separator/garbage line :: 63%</t>
+          <t>L345: symbol-only separator/garbage line :: 43%</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L355: isolated marker/symbol line :: !/</t>
+          <t>L223: isolated marker/symbol line :: L.</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr">
@@ -1709,7 +1737,7 @@
       </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>L623: punctuation artifact: repeated periods :: Balt, and Ohio....</t>
+          <t>L621: punctuation artifact: repeated periods :: Atchison...........</t>
         </is>
       </c>
       <c r="R17" s="1" t="inlineStr"/>
@@ -1734,19 +1762,19 @@
       <c r="J18" s="1" t="inlineStr"/>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>L369: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€ž</t>
+          <t>L1125: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: some interesting stereoptic view•</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L361: isolated marker/symbol line :: .</t>
+          <t>L353: isolated marker/symbol line :: 31</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L364: isolated marker/symbol line :: 66</t>
+          <t>L355: isolated marker/symbol line :: !/</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr">
@@ -1756,7 +1784,7 @@
       </c>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>L624: punctuation artifact: repeated periods :: B. R. T............</t>
+          <t>L623: punctuation artifact: repeated periods :: Balt, and Ohio....</t>
         </is>
       </c>
       <c r="R18" s="1" t="inlineStr"/>
@@ -1779,21 +1807,17 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L373: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: at 3.30 oâ€™clock. All members are request-</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L362: symbol-only separator/garbage line :: 128%</t>
+          <t>L356: symbol-only separator/garbage line :: 63%</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L458: symbol-only separator/garbage line :: 613.</t>
+          <t>L357: isolated marker/symbol line :: 1°</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr">
@@ -1803,7 +1827,7 @@
       </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>L626: punctuation artifact: repeated periods :: C. P. R............</t>
+          <t>L624: punctuation artifact: repeated periods :: B. R. T............</t>
         </is>
       </c>
       <c r="R19" s="1" t="inlineStr"/>
@@ -1826,21 +1850,17 @@
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L407: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: New York, Aug. 5.â€”The opening</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L367: isolated marker/symbol line :: :</t>
+          <t>L361: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L480: isolated marker/symbol line :: .</t>
+          <t>L364: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr">
@@ -1850,7 +1870,7 @@
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>L628: punctuation artifact: repeated periods :: Chesa. and Ohio..</t>
+          <t>L626: punctuation artifact: repeated periods :: C. P. R............</t>
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr"/>
@@ -1873,21 +1893,17 @@
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
       <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L423: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ton, Secâ€™y to Trustees, McGivney June-</t>
-        </is>
-      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L368: symbol-only separator/garbage line :: 110%</t>
+          <t>L362: symbol-only separator/garbage line :: 128%</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L516: isolated marker/symbol line :: 6</t>
+          <t>L369: isolated marker/symbol line :: „</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr">
@@ -1897,7 +1913,7 @@
       </c>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>L631: punctuation artifact: repeated periods :: Col Fuel and Iron..</t>
+          <t>L628: punctuation artifact: repeated periods :: Chesa. and Ohio..</t>
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr"/>
@@ -1920,21 +1936,17 @@
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L424: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: tion, N. B.â€”641 d</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L375: isolated marker/symbol line :: 36</t>
+          <t>L367: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L518: symbol-only separator/garbage line :: ;*******************************</t>
+          <t>L458: symbol-only separator/garbage line :: 613.</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr">
@@ -1944,7 +1956,7 @@
       </c>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>L633: punctuation artifact: repeated periods :: Chino Copper..</t>
+          <t>L631: punctuation artifact: repeated periods :: Col Fuel and Iron..</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr"/>
@@ -1967,31 +1979,27 @@
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L450: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: duced a good effect on sentiment. U. â€”â€”</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L381: symbol-only separator/garbage line :: . 96%</t>
+          <t>L368: symbol-only separator/garbage line :: 110%</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L532: symbol-only separator/garbage line :: *******************</t>
+          <t>L480: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
-          <t>L470: punctuation artifact: repeated periods :: ï¼š... 15%</t>
+          <t>L470: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | symbol-only separator/garbage line | punctuation artifact: repeated periods :: ：... 15%</t>
         </is>
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>L635: punctuation artifact: repeated periods :: Con. Gas.........</t>
+          <t>L633: punctuation artifact: repeated periods :: Chino Copper..</t>
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr"/>
@@ -2014,21 +2022,17 @@
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L451: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: LOSTâ€”Gentâ€™s gold watch fob.</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L382: symbol-only separator/garbage line :: 97%</t>
+          <t>L374: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | symbol-only separator/garbage line :: ： 36</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L545: isolated marker/symbol line :: 71</t>
+          <t>L516: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr">
@@ -2038,7 +2042,7 @@
       </c>
       <c r="Q24" s="1" t="inlineStr">
         <is>
-          <t>L637: punctuation artifact: repeated periods :: Erie..............</t>
+          <t>L635: punctuation artifact: repeated periods :: Con. Gas.........</t>
         </is>
       </c>
       <c r="R24" s="1" t="inlineStr"/>
@@ -2061,21 +2065,17 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L457: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1 will kindly leave at Gleaner officeâ€”1 in</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L387: isolated marker/symbol line :: 964</t>
+          <t>L375: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L546: symbol-only separator/garbage line :: 27%</t>
+          <t>L518: symbol-only separator/garbage line :: ;*******************************</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="Q25" s="1" t="inlineStr">
         <is>
-          <t>L639: punctuation artifact: repeated periods :: Erie, 1st Pfd.....</t>
+          <t>L637: punctuation artifact: repeated periods :: Erie..............</t>
         </is>
       </c>
       <c r="R25" s="1" t="inlineStr"/>
@@ -2108,21 +2108,17 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L505: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: requested to flâ€™e the same, duly attested,</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L392: symbol-only separator/garbage line :: . 88</t>
+          <t>L381: symbol-only separator/garbage line :: . 96%</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L548: isolated marker/symbol line :: 45</t>
+          <t>L532: symbol-only separator/garbage line :: *******************</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr">
@@ -2132,7 +2128,7 @@
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t>L641: punctuation artifact: repeated periods :: Gen. Elec..........</t>
+          <t>L639: punctuation artifact: repeated periods :: Erie, 1st Pfd.....</t>
         </is>
       </c>
       <c r="R26" s="1" t="inlineStr"/>
@@ -2155,21 +2151,17 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L520: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ TO MY PATRONS-I wish to take this op- â€¢ nity of thanking youâ€¢</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L393: isolated marker/symbol line :: 8</t>
+          <t>L382: symbol-only separator/garbage line :: 97%</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L550: symbol-only separator/garbage line :: 43%</t>
+          <t>L545: isolated marker/symbol line :: 71</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr">
@@ -2179,7 +2171,7 @@
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>L643: punctuation artifact: repeated periods :: Gr. Nor. Pfd.......</t>
+          <t>L641: punctuation artifact: repeated periods :: Gen. Elec..........</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr"/>
@@ -2202,21 +2194,17 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L521: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | line starts with punctuation glued to text :: .for the very generous patronage you have given me since I opened up myâ€¢</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L399: symbol-only separator/garbage line :: . 217%</t>
+          <t>L387: isolated marker/symbol line :: 964</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L552: symbol-only separator/garbage line :: 3132</t>
+          <t>L546: symbol-only separator/garbage line :: 27%</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr">
@@ -2226,7 +2214,7 @@
       </c>
       <c r="Q28" s="1" t="inlineStr">
         <is>
-          <t>L645: punctuation artifact: repeated periods :: Gr. Nor. Ore........</t>
+          <t>L643: punctuation artifact: repeated periods :: Gr. Nor. Pfd.......</t>
         </is>
       </c>
       <c r="R28" s="1" t="inlineStr"/>
@@ -2249,21 +2237,17 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L522: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Millinery Parlors in this city. The very sanguine way in which your sup- Y</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L400: symbol-only separator/garbage line :: 215%</t>
+          <t>L392: symbol-only separator/garbage line :: . 88</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L554: symbol-only separator/garbage line :: 63%</t>
+          <t>L548: isolated marker/symbol line :: 45</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr">
@@ -2273,7 +2257,7 @@
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>L647: punctuation artifact: repeated periods :: ill. Cent............</t>
+          <t>L645: punctuation artifact: repeated periods :: Gr. Nor. Ore........</t>
         </is>
       </c>
       <c r="R29" s="1" t="inlineStr"/>
@@ -2296,21 +2280,17 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L523: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ port has been given has surpassed my fullest expectations and has not onlyâ€¢</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L404: symbol-only separator/garbage line :: . 55</t>
+          <t>L393: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L556: symbol-only separator/garbage line :: 128%</t>
+          <t>L550: symbol-only separator/garbage line :: 43%</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr">
@@ -2320,7 +2300,7 @@
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>L649: punctuation artifact: repeated periods :: Int. Met............</t>
+          <t>L647: punctuation artifact: repeated periods :: ill. Cent............</t>
         </is>
       </c>
       <c r="R30" s="1" t="inlineStr"/>
@@ -2343,21 +2323,17 @@
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L525: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢select my stock for Fall from the leading British and American Millinery.</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L406: isolated marker/symbol line :: 55</t>
+          <t>L399: symbol-only separator/garbage line :: . 217%</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L558: symbol-only separator/garbage line :: 110%</t>
+          <t>L552: symbol-only separator/garbage line :: 3132</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr">
@@ -2367,7 +2343,7 @@
       </c>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>L651: punctuation artifact: repeated periods :: Louis, and Nash...</t>
+          <t>L649: punctuation artifact: repeated periods :: Int. Met............</t>
         </is>
       </c>
       <c r="R31" s="1" t="inlineStr"/>
@@ -2390,21 +2366,17 @@
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L526: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢centerusting to be favored with a continuance of your esteemed patronage,.</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L409: isolated marker/symbol line :: +</t>
+          <t>L400: symbol-only separator/garbage line :: 215%</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L560: isolated marker/symbol line :: 36</t>
+          <t>L554: symbol-only separator/garbage line :: 63%</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr">
@@ -2414,7 +2386,7 @@
       </c>
       <c r="Q32" s="1" t="inlineStr">
         <is>
-          <t>L653: punctuation artifact: repeated periods :: Lehigh Valley.......</t>
+          <t>L651: punctuation artifact: repeated periods :: Louis, and Nash...</t>
         </is>
       </c>
       <c r="R32" s="1" t="inlineStr"/>
@@ -2437,21 +2409,17 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L528: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Yours Very Respectfully,</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L412: symbol-only separator/garbage line :: 106%</t>
+          <t>L404: symbol-only separator/garbage line :: . 55</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L562: symbol-only separator/garbage line :: 97%</t>
+          <t>L556: symbol-only separator/garbage line :: 128%</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr">
@@ -2461,7 +2429,7 @@
       </c>
       <c r="Q33" s="1" t="inlineStr">
         <is>
-          <t>L655: punctuation artifact: repeated periods :: Kansas City So., ..</t>
+          <t>L653: punctuation artifact: repeated periods :: Lehigh Valley.......</t>
         </is>
       </c>
       <c r="R33" s="1" t="inlineStr"/>
@@ -2484,21 +2452,17 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L577: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 29% PEAK FREAN &amp; COâ€™S</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L418: symbol-only separator/garbage line :: . 31%</t>
+          <t>L405: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L564: symbol-only separator/garbage line :: 96%</t>
+          <t>L558: symbol-only separator/garbage line :: 110%</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr">
@@ -2508,7 +2472,7 @@
       </c>
       <c r="Q34" s="1" t="inlineStr">
         <is>
-          <t>L657: punctuation artifact: repeated periods :: Miss., Kan. and Tex.. .. 22%</t>
+          <t>L655: punctuation artifact: repeated periods :: Kansas City So., ..</t>
         </is>
       </c>
       <c r="R34" s="1" t="inlineStr"/>
@@ -2531,21 +2495,17 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L671: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L419: symbol-only separator/garbage line :: 31%</t>
+          <t>L406: isolated marker/symbol line :: 55</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L565: isolated marker/symbol line :: 8</t>
+          <t>L560: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr">
@@ -2555,7 +2515,7 @@
       </c>
       <c r="Q35" s="1" t="inlineStr">
         <is>
-          <t>L719: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 88</t>
+          <t>L657: punctuation artifact: repeated periods :: Miss., Kan. and Tex.. .. 22%</t>
         </is>
       </c>
       <c r="R35" s="1" t="inlineStr"/>
@@ -2578,21 +2538,17 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L728: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 75c (letter/digit mix) :: Pricesâ€”75c, $1.00, $1.50.</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L425: symbol-only separator/garbage line :: . 39%</t>
+          <t>L409: isolated marker/symbol line :: +</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L567: symbol-only separator/garbage line :: 215%</t>
+          <t>L562: symbol-only separator/garbage line :: 97%</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr">
@@ -2602,7 +2558,7 @@
       </c>
       <c r="Q36" s="1" t="inlineStr">
         <is>
-          <t>L756: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 31%</t>
+          <t>L719: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 88</t>
         </is>
       </c>
       <c r="R36" s="1" t="inlineStr"/>
@@ -2625,21 +2581,17 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L833: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: 1905 to 1911 with much satisfaction. Peopleâ€™s Gas...............................................</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L426: symbol-only separator/garbage line :: 39%</t>
+          <t>L411: isolated marker/symbol line :: ……</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L568: symbol-only separator/garbage line :: 55%</t>
+          <t>L564: symbol-only separator/garbage line :: 96%</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr">
@@ -2649,7 +2601,7 @@
       </c>
       <c r="Q37" s="1" t="inlineStr">
         <is>
-          <t>L758: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 39%</t>
+          <t>L756: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 31%</t>
         </is>
       </c>
       <c r="R37" s="1" t="inlineStr"/>
@@ -2672,27 +2624,23 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L841: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: of the Board of Health officially in-â€œSooâ€�</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L429: isolated marker/symbol line :: 131</t>
+          <t>L412: symbol-only separator/garbage line :: 106%</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L570: symbol-only separator/garbage line :: 106%</t>
+          <t>L565: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
       <c r="Q38" s="1" t="inlineStr">
         <is>
-          <t>L760: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...131%</t>
+          <t>L758: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 39%</t>
         </is>
       </c>
       <c r="R38" s="1" t="inlineStr"/>
@@ -2715,27 +2663,23 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L899: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the distance. â€œEvery reduction made</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L430: symbol-only separator/garbage line :: 131%</t>
+          <t>L418: symbol-only separator/garbage line :: . 31%</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L572: symbol-only separator/garbage line :: 31%</t>
+          <t>L567: symbol-only separator/garbage line :: 215%</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr">
         <is>
-          <t>L762: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...29%</t>
+          <t>L760: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...131%</t>
         </is>
       </c>
       <c r="R39" s="1" t="inlineStr"/>
@@ -2758,27 +2702,23 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L985: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Car Fdyâ€”15 at 67.</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L436: symbol-only separator/garbage line :: . 29%</t>
+          <t>L419: symbol-only separator/garbage line :: 31%</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L574: symbol-only separator/garbage line :: 39%</t>
+          <t>L568: symbol-only separator/garbage line :: 55%</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr">
         <is>
-          <t>L774: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...15% - - |</t>
+          <t>L762: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...29%</t>
         </is>
       </c>
       <c r="R40" s="1" t="inlineStr"/>
@@ -2801,27 +2741,23 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L993: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Cement Pfd.â€”2 at 89%. 31 at 90.</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L437: symbol-only separator/garbage line :: 29%</t>
+          <t>L425: symbol-only separator/garbage line :: . 39%</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L575: symbol-only separator/garbage line :: 131%</t>
+          <t>L570: symbol-only separator/garbage line :: 106%</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr">
         <is>
-          <t>L776: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...134% 134%</t>
+          <t>L774: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...15% - - |</t>
         </is>
       </c>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2844,27 +2780,23 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L995: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: C. P. R.â€”25 at 216%, 100 at 216%.</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L443: isolated marker/symbol line :: .</t>
+          <t>L426: symbol-only separator/garbage line :: 39%</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L579: symbol-only separator/garbage line :: 46%</t>
+          <t>L572: symbol-only separator/garbage line :: 31%</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr">
         <is>
-          <t>L778: symbol-only separator/garbage line | punctuation artifact: repeated periods :: , ..150% 151%</t>
+          <t>L776: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...134% 134%</t>
         </is>
       </c>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2887,27 +2819,23 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L1039: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Dom Ironâ€”160 at 44.</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L444: symbol-only separator/garbage line :: 46%</t>
+          <t>L429: isolated marker/symbol line :: 131</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L580: symbol-only separator/garbage line :: 140%</t>
+          <t>L574: symbol-only separator/garbage line :: 39%</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr">
         <is>
-          <t>L831: punctuation artifact: repeated periods :: Miss Katherine Haggarty (Sister Pac. Mail.......................................................</t>
+          <t>L778: symbol-only separator/garbage line | punctuation artifact: repeated periods :: , ..150% 151%</t>
         </is>
       </c>
       <c r="R43" s="1" t="inlineStr"/>
@@ -2930,27 +2858,23 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L1041: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Iron Pfd.â€”15 at 93%. 10 at 93%.</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L449: isolated marker/symbol line :: :</t>
+          <t>L430: symbol-only separator/garbage line :: 131%</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L582: symbol-only separator/garbage line :: 126%</t>
+          <t>L575: symbol-only separator/garbage line :: 131%</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr">
         <is>
-          <t>L832: punctuation artifact: repeated periods :: Clarice), who filled the position from penn ex div..............................................</t>
+          <t>L831: punctuation artifact: repeated periods :: Miss Katherine Haggarty (Sister Pac. Mail.......................................................</t>
         </is>
       </c>
       <c r="R44" s="1" t="inlineStr"/>
@@ -2973,27 +2897,23 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L1043: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Brazilâ€”35 at 85%.</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L450: symbol-only separator/garbage line :: 140%</t>
+          <t>L436: symbol-only separator/garbage line :: . 29%</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L584: symbol-only separator/garbage line :: 35%</t>
+          <t>L579: symbol-only separator/garbage line :: 46%</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
       <c r="Q45" s="1" t="inlineStr">
         <is>
-          <t>L833: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: 1905 to 1911 with much satisfaction. Peopleâ€™s Gas...............................................</t>
+          <t>L832: punctuation artifact: repeated periods :: Clarice), who filled the position from penn ex div..............................................</t>
         </is>
       </c>
       <c r="R45" s="1" t="inlineStr"/>
@@ -3016,27 +2936,23 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L1045: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Bridgeâ€”25 at 116.</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L455: symbol-only separator/garbage line :: . 125%</t>
+          <t>L437: symbol-only separator/garbage line :: 29%</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L586: isolated marker/symbol line :: 107</t>
+          <t>L580: symbol-only separator/garbage line :: 140%</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
       <c r="Q46" s="1" t="inlineStr">
         <is>
-          <t>L840: punctuation artifact: repeated periods :: evening meeting from the Secretary So Pacific...</t>
+          <t>L833: punctuation artifact: repeated periods :: 1905 to 1911 with much satisfaction. People’s Gas...............................................</t>
         </is>
       </c>
       <c r="R46" s="1" t="inlineStr"/>
@@ -3059,27 +2975,23 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L1047: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Scotiaâ€”25 at 73.</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L456: symbol-only separator/garbage line :: 126%</t>
+          <t>L443: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L601: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 71</t>
+          <t>L582: symbol-only separator/garbage line :: 126%</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr">
         <is>
-          <t>L842: punctuation artifact: repeated periods :: Sou. Ry...................................................</t>
+          <t>L840: punctuation artifact: repeated periods :: evening meeting from the Secretary So Pacific...</t>
         </is>
       </c>
       <c r="R47" s="1" t="inlineStr"/>
@@ -3102,27 +3014,23 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L1049: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Quebecâ€”20 at 12.</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L459: symbol-only separator/garbage line :: . 35%</t>
+          <t>L444: symbol-only separator/garbage line :: 46%</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L603: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 26%</t>
+          <t>L584: symbol-only separator/garbage line :: 35%</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
       <c r="Q48" s="1" t="inlineStr">
         <is>
-          <t>L843: punctuation artifact: repeated periods :: Utah Copper..</t>
+          <t>L842: punctuation artifact: repeated periods :: Sou. Ry...................................................</t>
         </is>
       </c>
       <c r="R48" s="1" t="inlineStr"/>
@@ -3145,27 +3053,23 @@
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L1051: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Span. Riverâ€”85 at 30, 250 at 40%,</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L460: symbol-only separator/garbage line :: 35%</t>
+          <t>L449: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L605: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 4%</t>
+          <t>L586: isolated marker/symbol line :: 107</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
       <c r="Q49" s="1" t="inlineStr">
         <is>
-          <t>L844: punctuation artifact: repeated periods :: Un. Pacific...</t>
+          <t>L843: punctuation artifact: repeated periods :: Utah Copper..</t>
         </is>
       </c>
       <c r="R49" s="1" t="inlineStr"/>
@@ -3188,27 +3092,23 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L1054: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Toronto Râ€™yâ€”25 at 138%2, 1 at 139.</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L465: symbol-only separator/garbage line :: . 106%</t>
+          <t>L450: symbol-only separator/garbage line :: 140%</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L607: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...42%</t>
+          <t>L601: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 71</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr"/>
       <c r="Q50" s="1" t="inlineStr">
         <is>
-          <t>L846: punctuation artifact: repeated periods :: U. S. Steel..</t>
+          <t>L844: punctuation artifact: repeated periods :: Un. Pacific...</t>
         </is>
       </c>
       <c r="R50" s="1" t="inlineStr"/>
@@ -3231,27 +3131,23 @@
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L1056: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ogilvieâ€”85 at 112.</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L466: isolated marker/symbol line :: 107</t>
+          <t>L455: symbol-only separator/garbage line :: . 125%</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr">
         <is>
-          <t>L667: symbol-only separator/garbage line :: 20%</t>
+          <t>L603: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 26%</t>
         </is>
       </c>
       <c r="P51" s="1" t="inlineStr"/>
       <c r="Q51" s="1" t="inlineStr">
         <is>
-          <t>L859: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..113% 112%</t>
+          <t>L846: punctuation artifact: repeated periods :: U. S. Steel..</t>
         </is>
       </c>
       <c r="R51" s="1" t="inlineStr"/>
@@ -3274,27 +3170,23 @@
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L1058: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Tuckettsâ€”5 at 40%.</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L471: isolated marker/symbol line :: .</t>
+          <t>L456: symbol-only separator/garbage line :: 126%</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr">
         <is>
-          <t>L669: symbol-only separator/garbage line :: 61%</t>
+          <t>L605: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 4%</t>
         </is>
       </c>
       <c r="P52" s="1" t="inlineStr"/>
       <c r="Q52" s="1" t="inlineStr">
         <is>
-          <t>L861: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..114% 114%</t>
+          <t>L859: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..113% 112%</t>
         </is>
       </c>
       <c r="R52" s="1" t="inlineStr"/>
@@ -3317,27 +3209,23 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L1060: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ottawaâ€”13 at 151.</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L477: symbol-only separator/garbage line :: 134134%</t>
+          <t>L459: symbol-only separator/garbage line :: . 35%</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr">
         <is>
-          <t>L671: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L607: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...42%</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr"/>
       <c r="Q53" s="1" t="inlineStr">
         <is>
-          <t>L863: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..159% 159%</t>
+          <t>L861: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..114% 114%</t>
         </is>
       </c>
       <c r="R53" s="1" t="inlineStr"/>
@@ -3360,27 +3248,23 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L1062: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Tex. Pfd.â€”1 at 99, 1 at 99%. 2 at</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L482: symbol-only separator/garbage line :: . 150</t>
+          <t>L460: symbol-only separator/garbage line :: 35%</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr">
         <is>
-          <t>L673: symbol-only separator/garbage line :: *********</t>
+          <t>L667: symbol-only separator/garbage line :: 20%</t>
         </is>
       </c>
       <c r="P54" s="1" t="inlineStr"/>
       <c r="Q54" s="1" t="inlineStr">
         <is>
-          <t>L919: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ......126% 127%</t>
+          <t>L863: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..159% 159%</t>
         </is>
       </c>
       <c r="R54" s="1" t="inlineStr"/>
@@ -3403,27 +3287,23 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L1065: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Bondsâ€”Coalâ€”1000 at 97.</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L483: isolated marker/symbol line :: 151</t>
+          <t>L465: symbol-only separator/garbage line :: . 106%</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr">
         <is>
-          <t>L713: symbol-only separator/garbage line :: .36</t>
+          <t>L669: symbol-only separator/garbage line :: 61%</t>
         </is>
       </c>
       <c r="P55" s="1" t="inlineStr"/>
       <c r="Q55" s="1" t="inlineStr">
         <is>
-          <t>L921: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 24% 24%</t>
+          <t>L919: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ......126% 127%</t>
         </is>
       </c>
       <c r="R55" s="1" t="inlineStr"/>
@@ -3446,27 +3326,23 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L1067: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Banksâ€”Commerceâ€”4 at 200; Royal</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L487: symbol-only separator/garbage line :: 27%</t>
+          <t>L466: isolated marker/symbol line :: 107</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr">
         <is>
-          <t>L715: symbol-only separator/garbage line :: .96%</t>
+          <t>L671: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P56" s="1" t="inlineStr"/>
       <c r="Q56" s="1" t="inlineStr">
         <is>
-          <t>L923: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 49% 49%</t>
+          <t>L921: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 24% 24%</t>
         </is>
       </c>
       <c r="R56" s="1" t="inlineStr"/>
@@ -3489,27 +3365,23 @@
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L1068: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 4a (letter/digit mix) :: â€”4a t 215; Nova Scotiaâ€”1.1 at 251;</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L491: isolated marker/symbol line :: 23</t>
+          <t>L470: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | symbol-only separator/garbage line | punctuation artifact: repeated periods :: ：... 15%</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr">
         <is>
-          <t>L717: symbol-only separator/garbage line :: .96</t>
+          <t>L673: symbol-only separator/garbage line :: *********</t>
         </is>
       </c>
       <c r="P57" s="1" t="inlineStr"/>
       <c r="Q57" s="1" t="inlineStr">
         <is>
-          <t>L925: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...149% 150%</t>
+          <t>L923: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 49% 49%</t>
         </is>
       </c>
       <c r="R57" s="1" t="inlineStr"/>
@@ -3532,27 +3404,23 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L1069: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Montreal-4 at 228; Molson;â€”5 at</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L494: symbol-only separator/garbage line :: . 32</t>
+          <t>L471: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr">
         <is>
-          <t>L719: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 88</t>
+          <t>L713: symbol-only separator/garbage line :: .36</t>
         </is>
       </c>
       <c r="P58" s="1" t="inlineStr"/>
       <c r="Q58" s="1" t="inlineStr">
         <is>
-          <t>L976: punctuation artifact: repeated periods :: Virginia Chem.........25%</t>
+          <t>L925: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...149% 150%</t>
         </is>
       </c>
       <c r="R58" s="1" t="inlineStr"/>
@@ -3575,27 +3443,23 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L1078: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ in order to ensure changes be-â€¢</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L495: symbol-only separator/garbage line :: 32%</t>
+          <t>L477: symbol-only separator/garbage line :: 134134%</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr">
         <is>
-          <t>L721: symbol-only separator/garbage line :: .217%</t>
+          <t>L715: symbol-only separator/garbage line :: .96%</t>
         </is>
       </c>
       <c r="P59" s="1" t="inlineStr"/>
       <c r="Q59" s="1" t="inlineStr">
         <is>
-          <t>L978: punctuation artifact: repeated periods :: Western Union...........</t>
+          <t>L976: punctuation artifact: repeated periods :: Virginia Chem.........25%</t>
         </is>
       </c>
       <c r="R59" s="1" t="inlineStr"/>
@@ -3618,25 +3482,25 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L1079: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ing made in advertisements,â€¢</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L499: isolated marker/symbol line :: 49</t>
+          <t>L482: symbol-only separator/garbage line :: . 150</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
         <is>
-          <t>L723: symbol-only separator/garbage line :: .55</t>
+          <t>L717: symbol-only separator/garbage line :: .96</t>
         </is>
       </c>
       <c r="P60" s="1" t="inlineStr"/>
-      <c r="Q60" s="1" t="inlineStr"/>
+      <c r="Q60" s="1" t="inlineStr">
+        <is>
+          <t>L978: punctuation artifact: repeated periods :: Western Union...........</t>
+        </is>
+      </c>
       <c r="R60" s="1" t="inlineStr"/>
       <c r="S60" s="1" t="inlineStr"/>
       <c r="T60" s="1" t="inlineStr"/>
@@ -3657,25 +3521,25 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L1080: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ copy must reach this office not â€¢</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L505: isolated marker/symbol line :: 110</t>
+          <t>L483: isolated marker/symbol line :: 151</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr">
         <is>
-          <t>L756: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 31%</t>
+          <t>L719: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 88</t>
         </is>
       </c>
       <c r="P61" s="1" t="inlineStr"/>
-      <c r="Q61" s="1" t="inlineStr"/>
+      <c r="Q61" s="1" t="inlineStr">
+        <is>
+          <t>L1078: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: ♦ in order to ensure changes be-•</t>
+        </is>
+      </c>
       <c r="R61" s="1" t="inlineStr"/>
       <c r="S61" s="1" t="inlineStr"/>
       <c r="T61" s="1" t="inlineStr"/>
@@ -3696,21 +3560,17 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L1081: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | localized OCR phrase divergence vs other OCR: "ofr" vs "of publication Hall s e MEATS AND Fi38" :: later than 9 a. m. on the day of â€¢</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L511: symbol-only separator/garbage line :: . 105</t>
+          <t>L487: symbol-only separator/garbage line :: 27%</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr">
         <is>
-          <t>L758: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 39%</t>
+          <t>L721: symbol-only separator/garbage line :: .217%</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr"/>
@@ -3735,21 +3595,17 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L1083: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ publication.â€¢</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L512: isolated marker/symbol line :: 105</t>
+          <t>L491: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
         <is>
-          <t>L760: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...131%</t>
+          <t>L723: symbol-only separator/garbage line :: .55</t>
         </is>
       </c>
       <c r="P63" s="1" t="inlineStr"/>
@@ -3774,21 +3630,17 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L1085: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Hallâ€™s</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L517: isolated marker/symbol line :: .</t>
+          <t>L494: symbol-only separator/garbage line :: . 32</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr">
         <is>
-          <t>L762: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...29%</t>
+          <t>L756: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 31%</t>
         </is>
       </c>
       <c r="P64" s="1" t="inlineStr"/>
@@ -3813,21 +3665,17 @@
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L1091: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Phone 244</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L519: symbol-only separator/garbage line :: . 20</t>
+          <t>L495: symbol-only separator/garbage line :: 32%</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr">
         <is>
-          <t>L768: symbol-only separator/garbage line :: .125%</t>
+          <t>L758: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 39%</t>
         </is>
       </c>
       <c r="P65" s="1" t="inlineStr"/>
@@ -3852,21 +3700,17 @@
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L1125: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: some interesting stereoptic viewâ€¢</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L520: isolated marker/symbol line :: .</t>
+          <t>L499: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr">
         <is>
-          <t>L770: symbol-only separator/garbage line :: .35%</t>
+          <t>L760: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...131%</t>
         </is>
       </c>
       <c r="P66" s="1" t="inlineStr"/>
@@ -3891,21 +3735,17 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L1160: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”DEALER INâ€”</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L526: symbol-only separator/garbage line :: . 113%</t>
+          <t>L505: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr">
         <is>
-          <t>L772: symbol-only separator/garbage line :: .106%</t>
+          <t>L762: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...29%</t>
         </is>
       </c>
       <c r="P67" s="1" t="inlineStr"/>
@@ -3935,12 +3775,12 @@
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L527: symbol-only separator/garbage line :: 112%</t>
+          <t>L511: symbol-only separator/garbage line :: . 105</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr">
         <is>
-          <t>L774: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...15% - - |</t>
+          <t>L768: symbol-only separator/garbage line :: .125%</t>
         </is>
       </c>
       <c r="P68" s="1" t="inlineStr"/>
@@ -3970,12 +3810,12 @@
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L533: symbol-only separator/garbage line :: . 114%</t>
+          <t>L512: isolated marker/symbol line :: 105</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr">
         <is>
-          <t>L776: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...134% 134%</t>
+          <t>L770: symbol-only separator/garbage line :: .35%</t>
         </is>
       </c>
       <c r="P69" s="1" t="inlineStr"/>
@@ -4005,12 +3845,12 @@
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L534: isolated marker/symbol line :: 114</t>
+          <t>L517: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr">
         <is>
-          <t>L778: symbol-only separator/garbage line | punctuation artifact: repeated periods :: , ..150% 151%</t>
+          <t>L772: symbol-only separator/garbage line :: .106%</t>
         </is>
       </c>
       <c r="P70" s="1" t="inlineStr"/>
@@ -4040,12 +3880,12 @@
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L540: symbol-only separator/garbage line :: 159% 159%</t>
+          <t>L519: symbol-only separator/garbage line :: . 20</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr">
         <is>
-          <t>L780: symbol-only separator/garbage line :: . 26%</t>
+          <t>L774: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...15% - - |</t>
         </is>
       </c>
       <c r="P71" s="1" t="inlineStr"/>
@@ -4075,12 +3915,12 @@
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L547: symbol-only separator/garbage line :: 23%</t>
+          <t>L520: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr">
         <is>
-          <t>L804: symbol-only separator/garbage line :: 27%</t>
+          <t>L776: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...134% 134%</t>
         </is>
       </c>
       <c r="P72" s="1" t="inlineStr"/>
@@ -4110,12 +3950,12 @@
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L554: symbol-only separator/garbage line :: . 17</t>
+          <t>L526: symbol-only separator/garbage line :: . 113%</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr">
         <is>
-          <t>L805: symbol-only separator/garbage line :: 23%</t>
+          <t>L778: symbol-only separator/garbage line | punctuation artifact: repeated periods :: , ..150% 151%</t>
         </is>
       </c>
       <c r="P73" s="1" t="inlineStr"/>
@@ -4145,12 +3985,12 @@
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L555: symbol-only separator/garbage line :: 16%</t>
+          <t>L527: symbol-only separator/garbage line :: 112%</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr">
         <is>
-          <t>L807: symbol-only separator/garbage line :: 32%</t>
+          <t>L780: symbol-only separator/garbage line :: . 26%</t>
         </is>
       </c>
       <c r="P74" s="1" t="inlineStr"/>
@@ -4180,12 +4020,12 @@
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L561: symbol-only separator/garbage line :: . 91%</t>
+          <t>L533: symbol-only separator/garbage line :: . 114%</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr">
         <is>
-          <t>L808: isolated marker/symbol line :: 49</t>
+          <t>L804: symbol-only separator/garbage line :: 27%</t>
         </is>
       </c>
       <c r="P75" s="1" t="inlineStr"/>
@@ -4215,12 +4055,12 @@
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L562: isolated marker/symbol line :: 92</t>
+          <t>L534: isolated marker/symbol line :: 114</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr">
         <is>
-          <t>L809: isolated marker/symbol line :: 110</t>
+          <t>L805: symbol-only separator/garbage line :: 23%</t>
         </is>
       </c>
       <c r="P76" s="1" t="inlineStr"/>
@@ -4250,12 +4090,12 @@
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L565: symbol-only separator/garbage line :: . 126%</t>
+          <t>L536: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr">
         <is>
-          <t>L811: symbol-only separator/garbage line :: 105%</t>
+          <t>L807: symbol-only separator/garbage line :: 32%</t>
         </is>
       </c>
       <c r="P77" s="1" t="inlineStr"/>
@@ -4285,12 +4125,12 @@
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L566: symbol-only separator/garbage line :: 127%</t>
+          <t>L540: symbol-only separator/garbage line :: 159% 159%</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr">
         <is>
-          <t>L859: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..113% 112%</t>
+          <t>L808: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="P78" s="1" t="inlineStr"/>
@@ -4320,12 +4160,12 @@
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L570: symbol-only separator/garbage line :: . 24</t>
+          <t>L546: isolated marker/symbol line :: ….</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr">
         <is>
-          <t>L861: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..114% 114%</t>
+          <t>L809: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="P79" s="1" t="inlineStr"/>
@@ -4355,12 +4195,12 @@
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L571: symbol-only separator/garbage line :: 24%</t>
+          <t>L547: symbol-only separator/garbage line :: 23%</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
-          <t>L863: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..159% 159%</t>
+          <t>L811: symbol-only separator/garbage line :: 105%</t>
         </is>
       </c>
       <c r="P80" s="1" t="inlineStr"/>
@@ -4390,12 +4230,12 @@
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L576: symbol-only separator/garbage line :: . 49%</t>
+          <t>L554: symbol-only separator/garbage line :: . 17</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr">
         <is>
-          <t>L867: symbol-only separator/garbage line :: 16%</t>
+          <t>L859: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..113% 112%</t>
         </is>
       </c>
       <c r="P81" s="1" t="inlineStr"/>
@@ -4425,12 +4265,12 @@
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L577: symbol-only separator/garbage line :: 49%</t>
+          <t>L555: symbol-only separator/garbage line :: 16%</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr">
         <is>
-          <t>L915: isolated marker/symbol line :: 17</t>
+          <t>L861: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..114% 114%</t>
         </is>
       </c>
       <c r="P82" s="1" t="inlineStr"/>
@@ -4460,12 +4300,12 @@
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L580: isolated marker/symbol line :: 1</t>
+          <t>L561: symbol-only separator/garbage line :: . 91%</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr">
         <is>
-          <t>L917: symbol-only separator/garbage line :: 91%</t>
+          <t>L863: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..159% 159%</t>
         </is>
       </c>
       <c r="P83" s="1" t="inlineStr"/>
@@ -4495,12 +4335,12 @@
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L583: symbol-only separator/garbage line :: . 149%</t>
+          <t>L562: isolated marker/symbol line :: 92</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr">
         <is>
-          <t>L919: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ......126% 127%</t>
+          <t>L867: symbol-only separator/garbage line :: 16%</t>
         </is>
       </c>
       <c r="P84" s="1" t="inlineStr"/>
@@ -4530,12 +4370,12 @@
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L584: isolated marker/symbol line :: 150</t>
+          <t>L565: symbol-only separator/garbage line :: . 126%</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr">
         <is>
-          <t>L921: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 24% 24%</t>
+          <t>L915: isolated marker/symbol line :: 17</t>
         </is>
       </c>
       <c r="P85" s="1" t="inlineStr"/>
@@ -4565,12 +4405,12 @@
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L588: symbol-only separator/garbage line :: 60%</t>
+          <t>L566: symbol-only separator/garbage line :: 127%</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr">
         <is>
-          <t>L923: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 49% 49%</t>
+          <t>L917: symbol-only separator/garbage line :: 91%</t>
         </is>
       </c>
       <c r="P86" s="1" t="inlineStr"/>
@@ -4600,12 +4440,12 @@
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L596: symbol-only separator/garbage line :: 60%</t>
+          <t>L570: symbol-only separator/garbage line :: . 24</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr">
         <is>
-          <t>L925: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...149% 150%</t>
+          <t>L919: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ......126% 127%</t>
         </is>
       </c>
       <c r="P87" s="1" t="inlineStr"/>
@@ -4635,12 +4475,12 @@
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L600: isolated marker/symbol line :: 107</t>
+          <t>L571: symbol-only separator/garbage line :: 24%</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr">
         <is>
-          <t>L927: symbol-only separator/garbage line :: 60 60%</t>
+          <t>L921: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 24% 24%</t>
         </is>
       </c>
       <c r="P88" s="1" t="inlineStr"/>
@@ -4670,12 +4510,12 @@
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L604: isolated marker/symbol line :: 426</t>
+          <t>L576: symbol-only separator/garbage line :: . 49%</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr">
         <is>
-          <t>L929: symbol-only separator/garbage line :: 60 60%</t>
+          <t>L923: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 49% 49%</t>
         </is>
       </c>
       <c r="P89" s="1" t="inlineStr"/>
@@ -4705,12 +4545,12 @@
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L609: symbol-only separator/garbage line :: 6514</t>
+          <t>L577: symbol-only separator/garbage line :: 49%</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr">
         <is>
-          <t>L931: symbol-only separator/garbage line :: 107%</t>
+          <t>L925: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...149% 150%</t>
         </is>
       </c>
       <c r="P90" s="1" t="inlineStr"/>
@@ -4740,12 +4580,12 @@
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L624: isolated marker/symbol line :: 600</t>
+          <t>L580: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr">
         <is>
-          <t>L933: isolated marker/symbol line :: 26</t>
+          <t>L927: symbol-only separator/garbage line :: 60 60%</t>
         </is>
       </c>
       <c r="P91" s="1" t="inlineStr"/>
@@ -4775,12 +4615,12 @@
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L679: isolated marker/symbol line :: â†’</t>
+          <t>L583: symbol-only separator/garbage line :: . 149%</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr">
         <is>
-          <t>L935: symbol-only separator/garbage line :: 65%</t>
+          <t>L929: symbol-only separator/garbage line :: 60 60%</t>
         </is>
       </c>
       <c r="P92" s="1" t="inlineStr"/>
@@ -4810,12 +4650,12 @@
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L682: symbol-only separator/garbage line :: 8.4</t>
+          <t>L584: isolated marker/symbol line :: 150</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr">
         <is>
-          <t>L937: symbol-only separator/garbage line :: 92%</t>
+          <t>L931: symbol-only separator/garbage line :: 107%</t>
         </is>
       </c>
       <c r="P93" s="1" t="inlineStr"/>
@@ -4845,12 +4685,12 @@
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L692: isolated marker/symbol line :: +</t>
+          <t>L588: symbol-only separator/garbage line :: 60%</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr">
         <is>
-          <t>L1012: symbol-only separator/garbage line | line starts with punctuation glued to text :: * 600</t>
+          <t>L933: isolated marker/symbol line :: 26</t>
         </is>
       </c>
       <c r="P94" s="1" t="inlineStr"/>
@@ -4880,12 +4720,12 @@
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L714: symbol-only separator/garbage line :: 100.</t>
+          <t>L596: symbol-only separator/garbage line :: 60%</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr">
         <is>
-          <t>L1037: isolated marker/symbol line :: N</t>
+          <t>L935: symbol-only separator/garbage line :: 65%</t>
         </is>
       </c>
       <c r="P95" s="1" t="inlineStr"/>
@@ -4915,12 +4755,12 @@
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L729: symbol-only separator/garbage line :: 188.</t>
+          <t>L600: isolated marker/symbol line :: 107</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr">
         <is>
-          <t>L1063: symbol-only separator/garbage line :: 100.</t>
+          <t>L937: symbol-only separator/garbage line :: 92%</t>
         </is>
       </c>
       <c r="P96" s="1" t="inlineStr"/>
@@ -4948,10 +4788,14 @@
       <c r="K97" s="1" t="inlineStr"/>
       <c r="L97" s="1" t="inlineStr"/>
       <c r="M97" s="1" t="inlineStr"/>
-      <c r="N97" s="1" t="inlineStr"/>
+      <c r="N97" s="1" t="inlineStr">
+        <is>
+          <t>L604: isolated marker/symbol line :: 426</t>
+        </is>
+      </c>
       <c r="O97" s="1" t="inlineStr">
         <is>
-          <t>L1070: symbol-only separator/garbage line :: 188.</t>
+          <t>L1012: symbol-only separator/garbage line | line starts with punctuation glued to text :: * 600</t>
         </is>
       </c>
       <c r="P97" s="1" t="inlineStr"/>
@@ -4979,10 +4823,14 @@
       <c r="K98" s="1" t="inlineStr"/>
       <c r="L98" s="1" t="inlineStr"/>
       <c r="M98" s="1" t="inlineStr"/>
-      <c r="N98" s="1" t="inlineStr"/>
+      <c r="N98" s="1" t="inlineStr">
+        <is>
+          <t>L609: symbol-only separator/garbage line :: 6514</t>
+        </is>
+      </c>
       <c r="O98" s="1" t="inlineStr">
         <is>
-          <t>L1075: symbol-only separator/garbage line :: 8.4</t>
+          <t>L1037: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="P98" s="1" t="inlineStr"/>
@@ -5010,10 +4858,14 @@
       <c r="K99" s="1" t="inlineStr"/>
       <c r="L99" s="1" t="inlineStr"/>
       <c r="M99" s="1" t="inlineStr"/>
-      <c r="N99" s="1" t="inlineStr"/>
+      <c r="N99" s="1" t="inlineStr">
+        <is>
+          <t>L612: stray/suspicious non-ASCII glyph(s): U+6E90 CJK UNIFIED IDEOGRAPH-6E90 | isolated marker/symbol line :: 源</t>
+        </is>
+      </c>
       <c r="O99" s="1" t="inlineStr">
         <is>
-          <t>L1087: isolated marker/symbol line :: e</t>
+          <t>L1063: symbol-only separator/garbage line :: 100.</t>
         </is>
       </c>
       <c r="P99" s="1" t="inlineStr"/>
@@ -5041,10 +4893,14 @@
       <c r="K100" s="1" t="inlineStr"/>
       <c r="L100" s="1" t="inlineStr"/>
       <c r="M100" s="1" t="inlineStr"/>
-      <c r="N100" s="1" t="inlineStr"/>
+      <c r="N100" s="1" t="inlineStr">
+        <is>
+          <t>L624: isolated marker/symbol line :: 600</t>
+        </is>
+      </c>
       <c r="O100" s="1" t="inlineStr">
         <is>
-          <t>L1127: isolated marker/symbol line :: e</t>
+          <t>L1070: symbol-only separator/garbage line :: 188.</t>
         </is>
       </c>
       <c r="P100" s="1" t="inlineStr"/>
@@ -5072,10 +4928,14 @@
       <c r="K101" s="1" t="inlineStr"/>
       <c r="L101" s="1" t="inlineStr"/>
       <c r="M101" s="1" t="inlineStr"/>
-      <c r="N101" s="1" t="inlineStr"/>
+      <c r="N101" s="1" t="inlineStr">
+        <is>
+          <t>L679: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
+        </is>
+      </c>
       <c r="O101" s="1" t="inlineStr">
         <is>
-          <t>L1192: isolated marker/symbol line :: -</t>
+          <t>L1075: symbol-only separator/garbage line :: 8.4</t>
         </is>
       </c>
       <c r="P101" s="1" t="inlineStr"/>
@@ -5103,10 +4963,14 @@
       <c r="K102" s="1" t="inlineStr"/>
       <c r="L102" s="1" t="inlineStr"/>
       <c r="M102" s="1" t="inlineStr"/>
-      <c r="N102" s="1" t="inlineStr"/>
+      <c r="N102" s="1" t="inlineStr">
+        <is>
+          <t>L682: symbol-only separator/garbage line :: 8.4</t>
+        </is>
+      </c>
       <c r="O102" s="1" t="inlineStr">
         <is>
-          <t>L1205: isolated marker/symbol line :: 0</t>
+          <t>L1087: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="P102" s="1" t="inlineStr"/>
@@ -5134,10 +4998,14 @@
       <c r="K103" s="1" t="inlineStr"/>
       <c r="L103" s="1" t="inlineStr"/>
       <c r="M103" s="1" t="inlineStr"/>
-      <c r="N103" s="1" t="inlineStr"/>
+      <c r="N103" s="1" t="inlineStr">
+        <is>
+          <t>L692: isolated marker/symbol line :: +</t>
+        </is>
+      </c>
       <c r="O103" s="1" t="inlineStr">
         <is>
-          <t>L1211: isolated marker/symbol line :: U</t>
+          <t>L1127: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="P103" s="1" t="inlineStr"/>
@@ -5151,6 +5019,111 @@
       <c r="X103" s="1" t="inlineStr"/>
       <c r="Y103" s="1" t="inlineStr"/>
     </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr"/>
+      <c r="B104" s="1" t="inlineStr"/>
+      <c r="C104" s="1" t="inlineStr"/>
+      <c r="D104" s="1" t="inlineStr"/>
+      <c r="E104" s="1" t="inlineStr"/>
+      <c r="F104" s="1" t="inlineStr"/>
+      <c r="G104" s="1" t="inlineStr"/>
+      <c r="H104" s="1" t="inlineStr"/>
+      <c r="I104" s="1" t="inlineStr"/>
+      <c r="J104" s="1" t="inlineStr"/>
+      <c r="K104" s="1" t="inlineStr"/>
+      <c r="L104" s="1" t="inlineStr"/>
+      <c r="M104" s="1" t="inlineStr"/>
+      <c r="N104" s="1" t="inlineStr">
+        <is>
+          <t>L714: symbol-only separator/garbage line :: 100.</t>
+        </is>
+      </c>
+      <c r="O104" s="1" t="inlineStr">
+        <is>
+          <t>L1192: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
+      <c r="P104" s="1" t="inlineStr"/>
+      <c r="Q104" s="1" t="inlineStr"/>
+      <c r="R104" s="1" t="inlineStr"/>
+      <c r="S104" s="1" t="inlineStr"/>
+      <c r="T104" s="1" t="inlineStr"/>
+      <c r="U104" s="1" t="inlineStr"/>
+      <c r="V104" s="1" t="inlineStr"/>
+      <c r="W104" s="1" t="inlineStr"/>
+      <c r="X104" s="1" t="inlineStr"/>
+      <c r="Y104" s="1" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr"/>
+      <c r="B105" s="1" t="inlineStr"/>
+      <c r="C105" s="1" t="inlineStr"/>
+      <c r="D105" s="1" t="inlineStr"/>
+      <c r="E105" s="1" t="inlineStr"/>
+      <c r="F105" s="1" t="inlineStr"/>
+      <c r="G105" s="1" t="inlineStr"/>
+      <c r="H105" s="1" t="inlineStr"/>
+      <c r="I105" s="1" t="inlineStr"/>
+      <c r="J105" s="1" t="inlineStr"/>
+      <c r="K105" s="1" t="inlineStr"/>
+      <c r="L105" s="1" t="inlineStr"/>
+      <c r="M105" s="1" t="inlineStr"/>
+      <c r="N105" s="1" t="inlineStr">
+        <is>
+          <t>L729: symbol-only separator/garbage line :: 188.</t>
+        </is>
+      </c>
+      <c r="O105" s="1" t="inlineStr">
+        <is>
+          <t>L1205: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
+      <c r="P105" s="1" t="inlineStr"/>
+      <c r="Q105" s="1" t="inlineStr"/>
+      <c r="R105" s="1" t="inlineStr"/>
+      <c r="S105" s="1" t="inlineStr"/>
+      <c r="T105" s="1" t="inlineStr"/>
+      <c r="U105" s="1" t="inlineStr"/>
+      <c r="V105" s="1" t="inlineStr"/>
+      <c r="W105" s="1" t="inlineStr"/>
+      <c r="X105" s="1" t="inlineStr"/>
+      <c r="Y105" s="1" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr"/>
+      <c r="B106" s="1" t="inlineStr"/>
+      <c r="C106" s="1" t="inlineStr"/>
+      <c r="D106" s="1" t="inlineStr"/>
+      <c r="E106" s="1" t="inlineStr"/>
+      <c r="F106" s="1" t="inlineStr"/>
+      <c r="G106" s="1" t="inlineStr"/>
+      <c r="H106" s="1" t="inlineStr"/>
+      <c r="I106" s="1" t="inlineStr"/>
+      <c r="J106" s="1" t="inlineStr"/>
+      <c r="K106" s="1" t="inlineStr"/>
+      <c r="L106" s="1" t="inlineStr"/>
+      <c r="M106" s="1" t="inlineStr"/>
+      <c r="N106" s="1" t="inlineStr">
+        <is>
+          <t>L768: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
+        </is>
+      </c>
+      <c r="O106" s="1" t="inlineStr">
+        <is>
+          <t>L1211: isolated marker/symbol line :: U</t>
+        </is>
+      </c>
+      <c r="P106" s="1" t="inlineStr"/>
+      <c r="Q106" s="1" t="inlineStr"/>
+      <c r="R106" s="1" t="inlineStr"/>
+      <c r="S106" s="1" t="inlineStr"/>
+      <c r="T106" s="1" t="inlineStr"/>
+      <c r="U106" s="1" t="inlineStr"/>
+      <c r="V106" s="1" t="inlineStr"/>
+      <c r="W106" s="1" t="inlineStr"/>
+      <c r="X106" s="1" t="inlineStr"/>
+      <c r="Y106" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
